--- a/data/output/evaluasi_31.xlsx
+++ b/data/output/evaluasi_31.xlsx
@@ -8,7 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="3100" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="3173" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="3101" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="3171" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="3173" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="3172" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +479,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>9.997075457466305</v>
+        <v>10.16247931005179</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -485,7 +488,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -504,7 +507,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>7.408610368779596</v>
+        <v>7.709290766544193</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -513,7 +516,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -528,20 +531,48 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.03491867757141945</v>
+        <v>7.824041172736522</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkrt_q1-25 vs implisit_q-to-q_pkrt_q1-25.1</t>
+          <t>adhb_net_ekspor_q3-25</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dki Jakarta</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>20.94699259049397</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25 vs y-on-y_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
         </is>
       </c>
     </row>
@@ -556,7 +587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -593,85 +624,363 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3173</v>
+        <v>3101</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kota Jakarta Pusat</t>
+          <t>Kabupaten Kepulauan Seribu</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21573394.77866286</v>
+        <v>-3.046904282366639</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q1-25_ril vs adhk_net_ekspor_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3173</v>
+        <v>3101</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kota Jakarta Pusat</t>
+          <t>Kabupaten Kepulauan Seribu</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-2.66689255597827</v>
+        <v>-3.161572547857226</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>sog_q_net_ekspor_q1-25_ril vs sog_q_net_ekspor_q1-25_rev</t>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>3101</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Seribu</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-2.320761206413825</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3101</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Seribu</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-4.388601026226314</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3171</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.4553894180635066</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3171</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>3.308392905593831</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>3173</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Kota Jakarta Pusat</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>-9.859846896639048</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_net_ekspor_q1-25_ril vs sog_y-on-y_net_ekspor_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Growth revisi berlawanan arah</t>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-1.088493296059313</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3172</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Timur</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>5.014239928137666</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>

--- a/data/output/evaluasi_31.xlsx
+++ b/data/output/evaluasi_31.xlsx
@@ -572,7 +572,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
